--- a/data/daily/2026-09/2026-09-24.xlsx
+++ b/data/daily/2026-09/2026-09-24.xlsx
@@ -1170,14 +1170,39 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1192,17 +1217,42 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,17 +1267,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,17 +1292,42 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1267,17 +1342,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1292,110 +1367,35 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1425,52 +1425,102 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1478,49 +1528,74 @@
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1528,129 +1603,54 @@
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -2600,18 +2600,22 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>선물용 만족도 높음 — 받는 사람의 기분을 좋게 하고 선물용으로 매우 만족스러움</t>
+          <t>선물용 높은 만족도 — 받았을 때 기분이 좋아지고 선물하기에 매우 적합함</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>피로 회복 및 컨디션 개선 — 섭취 후 피로가 풀리고 컨디션과 면역력 회복에 도움을 줌</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>피로 회복 및 건강 개선 — 무기력함이나 피로를 해소하고 건강 증진에 도움 됨</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>꼼꼼하고 안전한 포장 — 제품 포장 상태가 잘되어 안전하게 도착함</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>부담스러운 가격 — 멀티비타민 가격이 다소 비싸게 느껴짐</t>
+          <t>다소 높은 가격 부담 — 가격이 다소 비싸서 직접 구매 시 부담이 있음</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
@@ -2659,17 +2663,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>액상형으로 간편한 섭취 — 액상 제형이라 챙겨 먹기 쉽고 간편함</t>
+          <t>간편한 액상형 섭취 — 액상 비타민이라 챙겨 먹기 쉽고 간편함</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>활력 충전 및 피로 회복 — 피곤할 때 섭취 시 활력이 도는 듯한 느낌을 줌</t>
+          <t>활력 증진 및 피로 회복 — 복용 후 활력이 생기고 피로 해소에 도움이 됨</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>정성스러운 선물 구성 — 추석 카드와 추가 증정품이 포함되어 선물용으로 매우 만족스러움</t>
+          <t>고급스러운 선물 구성 — 패키지가 고급스럽고 메시지 카드 및 추가 증정이 있음</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -2718,21 +2722,25 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>탁월한 피로 감소 효과 — 섭취 후 피곤함이 줄어들고 에너지를 얻는 데 도움을 줌</t>
+          <t>우수한 피로 회복 효과 — 섭취 후 피곤함이 줄고 에너지가 생기는 효과가 있음</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>고급스러운 선물 패키지 — 명절 케이스 디자인이 고급스러워 선물용으로 적합함</t>
+          <t>고급스러운 선물용 패키지 — 명절 및 생일 선물용으로 구성과 포장이 우수함</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>선물용 쇼핑백 불량 — 함께 전달된 쇼핑백이 훼손되어 그대로 사용하기 어려움</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
+          <t>쇼핑백 품질 손상 — 함께 제공된 백이 훼손되어 받침으로 사용이 불가능함</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>높은 가격대 형성 — 가격이 비싸서 본인 구매용으로는 부담이 큼</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr"/>
     </row>
     <row r="5" ht="38" customHeight="1">
@@ -2777,18 +2785,22 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>개별 포장의 편리함 — 한 포씩 포장되어 있어 책상이나 가방에 넣고 챙기기 용이함</t>
+          <t>개별 포장의 편의성 — 한 포씩 개별 포장되어 휴대하며 챙기기 편함</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>빠른 피로 회복 — 피로가 쌓였을 때 마시면 힘이 나고 피로가 풀림</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>체력 및 피로 개선 — 피로가 쌓였을 때 마시면 체력 회복과 힘이 생김</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>고급스러운 포장 상태 — 포장 상태가 깔끔하고 고급스러워 선물용으로 적합함</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>배송 요청사항 미반영 — 관리실 위탁 사전 요청에도 불구하고 문 앞에 두고 배송됨</t>
+          <t>배송 요청사항 미반영 — 관리실 위탁 요청에도 불구하고 문 앞에 두고 감</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
@@ -2832,19 +2844,23 @@
         <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>빠른 배송과 알찬 포장 — 배송이 빠르고 추가 종이봉투가 동봉되어 선물용으로 적합함</t>
+          <t>신속한 배송 서비스 — 명절 연휴에도 배송이 빠르게 완료됨</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>컨디션 유지 및 활력 증진 — 여행이나 피로 시 섭취하면 활력이 생기고 하루 컨디션 유지에 좋음</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>쇼핑백 포함 알찬 구성 — 추가 종이봉투와 쇼핑백이 포함되어 선물용으로 양호함</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>컨디션 회복 효과 — 피로와 활력이 필요할 때 먹으면 하루 컨디션 유지에 좋음</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -2852,7 +2868,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -2860,54 +2876,62 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
+          <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>뉴트리포유</t>
+          <t>정관장</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19,900원</t>
+          <t>33,000원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/10056171</t>
+          <t>https://gift.kakao.com/product/12159594</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260219100848_1c2cc8073bd44eaab9f09d6b8fb8f34c.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260812135521_25667cc1efc34a698d1813fe75189344.jpg</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>8716</v>
+        <v>1675</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>빠른 에너징 및 체력 증진 — 섭취 후 피로감이 가시고 쌩쌩해질 정도로 체력 회복에 좋음</t>
+          <t>예쁘고 고급스러운 포장 — 포장이 정성스럽고 고급스러워 지인 선물용으로 적합함</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>꼼꼼한 포장과 휴대의 용이성 — 포장이 예쁘고 꼼꼼하며 휴대하며 챙겨 먹기 편함</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>높은 브랜드 신뢰도 — 정관장 브랜드라 품질을 믿고 구매 가능함</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>맛과 섭취 편의성 — 개별 포장되어 섭취가 간편하고 맛도 우수함</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>야간 복용 시 수면 방해 — 저녁 늦게 복용할 경우 숙면에 방해가 될 수 있음</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -2915,48 +2939,48 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
+          <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>정관장</t>
+          <t>뉴트리포유</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>33,000원</t>
+          <t>19,900원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12159594</t>
+          <t>https://gift.kakao.com/product/10056171</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260812135521_25667cc1efc34a698d1813fe75189344.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260219100848_1c2cc8073bd44eaab9f09d6b8fb8f34c.jpg</t>
         </is>
       </c>
       <c r="I8" t="n">
         <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>1675</v>
+        <v>8718</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>간편한 개별 포장 — 낱개로 개별 포장되어 있어 간편하게 챙겨 먹기 편리함</t>
+          <t>활력 및 에너지를 제공 — 섭취 후 피로가 줄고 생기 있게 활동하는 데 도움이 됨</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>브랜드 신뢰도 및 효과 — 정관장 브랜드 제품이라 신뢰가 가며 피로 회복 효과가 있음</t>
+          <t>맛있는 오렌지 맛 — 오렌지 맛으로 맛있게 먹을 수 있어 거부감이 없음</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>고급스러운 선물용 패키지 — 포장이 예쁘고 고급스러워 선물용으로 만족도가 높음</t>
+          <t>휴대성 및 꼼꼼한 포장 — 휴대가 용이하며 포장이 꼼꼼하게 도착함</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -2974,48 +2998,60 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[센트룸] 맛있는 멀티비타민 미네랄 멀티구미 (80구미)</t>
+          <t>"한국인 맞춤 명품 비타민" 옵티젠 이뮨 멀티비타민&amp;미네랄 30입 / 1박스 (+GIFT 쇼핑백)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>센트룸</t>
+          <t>옵티젠</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>24,000원</t>
+          <t>59,900원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7320451</t>
+          <t>https://gift.kakao.com/product/11090567</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260901110153_bb9a8b1870e2492e99dbbf1747444c66.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260904193818_f59d395f51c84f2da56ebd3fc14b52f2.jpg</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>6486</v>
+        <v>211</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>뛰어난 맛과 간편한 식감 — 맛있는 젤리 형태라 거부감 없이 간식처럼 맛있게 섭취함</t>
+          <t>간편한 통합 섭취 방식 — 액상과 정제를 한 번에 마실 수 있어 아침에도 간편함</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>물 없이 간편한 섭취 — 구미 제형이라 물 없이도 출근길이나 어디서나 먹기 편함</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+          <t>체력 관리 및 피로 완화 — 잠이 부족하거나 체력이 떨어질 때 먹으면 효과적임</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>정성스러운 패키징 — 정성스러운 선물 패키지로 구성되어 받는 사람 만족도가 높음</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>제품 먼지 오염 상태 — 택배 수령 시 쇼핑백과 상자에 먼지가 가득 묻어있음</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>밀봉 스티커 훼손 문제 — 밀봉 스티커가 떼어졌다 붙은 자국과 이물질이 남아있음</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr"/>
     </row>
     <row r="10" ht="38" customHeight="1">
@@ -3029,51 +3065,51 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>"한국인 맞춤 명품 비타민" 옵티젠 이뮨 멀티비타민&amp;미네랄 30입 / 1박스 (+GIFT 쇼핑백)</t>
+          <t>[센트룸] 맛있는 멀티비타민 미네랄 멀티구미 (80구미)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>옵티젠</t>
+          <t>센트룸</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>59,900원</t>
+          <t>24,000원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/11090567</t>
+          <t>https://gift.kakao.com/product/7320451</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260904193818_f59d395f51c84f2da56ebd3fc14b52f2.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260901110153_bb9a8b1870e2492e99dbbf1747444c66.jpg</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>211</v>
+        <v>6486</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>피로 완화 및 컨디션 관리 — 하루 하나씩 챙겨 먹으면 피로감이 줄어들고 건강 관리에 도움을 줌</t>
+          <t>맛있는 젤리 형태 — 영양제 느낌 없이 일반 젤리처럼 맛있게 먹을 수 있음</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>정성스러운 선물 구성 — 포장이 고급스럽고 빠른 배송과 구성으로 선물용에 만족함</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>배송 상태 및 위생 불량 — 상자 및 쇼핑백에 먼지가 가득하거나 개봉 스티커에 손자국이 묻어 있음</t>
-        </is>
-      </c>
+          <t>물 없이 간편한 복용 — 구미 타입이라 물이 없어도 어디서나 챙겨 먹기 편리함</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>귀엽고 깔끔한 패키지 — 패키지가 귀엽고 깔끔하여 가벼운 선물용으로 추천함</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
@@ -3119,18 +3155,22 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>성별 맞춤 선택 가능 — 남성용과 여성용을 선택할 수 있어 기호에 맞춘 선물이 가능함</t>
+          <t>성별 맞춤 영양 설계 — 성별 옵션 선택이 가능하며 풍부한 영양 성분을 함유함</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>지속적인 피로 완화 — 꾸준히 먹으면 피로감이 줄어들고 컨디션이 오래 유지됨</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>깔끔하고 정성스러운 포장 — 정성이 담긴 깔끔한 포장으로 선물용 가치가 높음</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>피로 해소 지속성 — 꾸준히 복용 시 덜 피곤하고 활력이 오래 유지됨</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>다소 큰 알약 크기 — 기존 제품 대비 정제 크기가 커서 삼키기 다소 힘듦</t>
+          <t>큰 알약 제형 부담 — 기존 제품 대비 알약 크기가 커서 삼키기 다소 힘듦</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -3178,18 +3218,22 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>고급스러운 패키지 디자인 — 틴케이스와 보자기, 박스 포장이 정성스럽고 예쁨</t>
+          <t>화려하고 고급스러운 포장 — 보자기와 틴케이스 등 선물 포장이 매우 아름답고 정성스러움</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>비리지 않고 맛있는 제형 — 콜라겐 특유의 비린 맛이 없고 낱개 앰플 형태로 먹기 편함</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>비리지 않고 맛있는 맛 — 콜라겐 특유의 비린 맛이 없고 맛있어서 부담 없음</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>1병 단위 개별 포장 — 앰플 형태로 하나씩 따서 먹을 수 있어 간편함</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>부담스러운 가격대 — 제품 가격이 다소 비싸고 지속해서 가격이 상승함</t>
+          <t>가격대에 대한 부담 — 지속적인 가격 상승 및 기본 가격대가 비싼 편임</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -3237,18 +3281,18 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>우수한 가성비 — 저렴한 가격에 풍부한 수량을 구매할 수 있음</t>
+          <t>부드럽고 다양한 맛 — 식감이 부드럽고 질리지 않는 다양한 맛 구성임</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>부드러운 식감과 다양한 맛 — 닭가슴살이 부드럽고 맛이 다양하여 질리지 않고 식단 관리가 가능함</t>
+          <t>뛰어난 가성비 자랑 — 저렴한 가격에 많은 양을 구매할 수 있어 만족스러움</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>배송 중 해동 발생 — 냉동 상품이 유지되지 않고 전부 녹아서 배송됨</t>
+          <t>배송 중 해동 발생 — 배송을 받았을 때 제품이 녹아있는 상태였음</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -3296,20 +3340,20 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>속 편한 소화 개선 — 식후 섭취 시 소화가 잘 되고 속이 편안해짐</t>
+          <t>속이 편한 소화 효과 — 식후 섭취 시 더부룩함이 없고 소화에 많은 도움이 됨</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>부담 없는 맛과 식감 — 고구마 맛 등으로 거부감 없이 맛있고 편하게 먹을 수 있음</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>증정품 크기 아쉬움 — 증정된 단백질칩 사은품의 크기가 다소 작음</t>
-        </is>
-      </c>
+          <t>고구마 맛의 우수한 풍미 — 거부감 없는 고소한 고구마 맛이라 먹기 편함</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>풍성한 증정 및 방송 혜택 — 라이브 방송 및 행사 구매 시 혜택과 사은품이 훌륭함</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
     </row>
@@ -3355,15 +3399,19 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>속이 편안해지는 효소 효과 — 매일 한 포씩 먹으면 속이 편해지고 추천하기 좋음</t>
+          <t>소화 개선 및 속 편함 — 꾸준히 섭취 시 속이 편안해져 만족도가 높음</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>저렴한 가격과 알찬 구성 — 할인가로 부담 없이 구매 가능하며 사은품과 유통기한도 넉넉함</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
+          <t>알찬 구성 및 긴 유통기한 — 유통기한이 넉넉하며 사은품과 가격 구성이 좋음</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>정성 가득한 포장 — 포장에 정성이 느껴져 선물용으로 받거나 주기에 좋음</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
@@ -3371,7 +3419,7 @@
     <row r="16" ht="38" customHeight="1">
       <c r="B16" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -3379,58 +3427,62 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1</t>
+          <t>[리센느에디션] 베리말차 캡슐레이션 효소 1.8g 30포, 2개</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>셀렉스</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>28,900원</t>
+          <t>24,900원</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13550266</t>
+          <t>https://gift.kakao.com/product/14208051</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260907094509_48a662610e174029823081c612ed4755.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260908134122_cb4724fa4d2d4e45b370faede2a463a5.jpg</t>
         </is>
       </c>
       <c r="I16" t="n">
         <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>214</v>
+        <v>101</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>단백질 특유의 비린 맛 없음 — 비리거나 텁텁하지 않고 진한 초코우유처럼 맛있게 마실 수 있음</t>
+          <t>맛있는 맛과 식감 — 말차 맛이 고소하고 동봉된 단백질바도 맛이 양호함</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>든든한 포만감 제공 — 마신 뒤 포만감이 느껴져 운동 후나 허기질 때 간식용으로 좋음</t>
+          <t>더부룩함 없는 소화 — 식단 관리나 식후 복용 시 속이 편안해짐</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>부드럽고 편안한 속 — 목넘김이 부드럽고 마신 후 속이 더부룩하지 않음</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>만족스러운 사은품 구성 — 포토카드 및 단백질바 포함 구성의 가성비가 훌륭함</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>다소 느린 배송 속도 — 배송 진행 속도가 다소 늦어 아쉬움이 있음</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
     </row>
     <row r="17" ht="38" customHeight="1">
       <c r="B17" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -3438,51 +3490,51 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[리센느에디션] 베리말차 캡슐레이션 효소 1.8g 30포, 2개</t>
+          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>셀렉스</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>24,900원</t>
+          <t>28,900원</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/14208051</t>
+          <t>https://gift.kakao.com/product/13550266</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260908134122_cb4724fa4d2d4e45b370faede2a463a5.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260907094509_48a662610e174029823081c612ed4755.jpg</t>
         </is>
       </c>
       <c r="I17" t="n">
         <v>4</v>
       </c>
       <c r="J17" t="n">
-        <v>99</v>
+        <v>214</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>속 편한 소화 및 더부룩함 완화 — 섭취 후 더부룩한 속이 편안해지는 느낌을 받음</t>
+          <t>비리지 않은 달콤한 맛 — 단백질 음료 특유의 비린 맛과 텁텁함이 없음</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>고소하고 맛있는 맛 — 베리말차 맛이 고소하고 맛있어 간편하게 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>배송 지연 아쉬움 — 배송이 다소 늦게 도착함</t>
-        </is>
-      </c>
+          <t>부드러운 목넘김과 포만감 — 목넘김이 부드럽고 적당한 포만감을 제공함</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>슬림한 용기의 휴대성 — 패키지가 슬림하여 가방에 넣어 다니기 편리함</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
     </row>
@@ -3528,16 +3580,20 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>고급스럽고 예쁜 포장 — 앰플 용기와 박스 포장이 예쁘고 고급스러움</t>
+          <t>고급스러운 앰플 디자인 — 용기와 포장이 공주풍으로 고급스럽고 예쁨</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>부담 없는 맛있는 제형 — 비타민 음료처럼 맛이 좋아 거부감 없이 마실 수 있음</t>
+          <t>알약 대비 쉬운 섭취 — 앰플 형태로 알약을 먹기 힘들어하는 사람에게 편함</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>진한 맛에 대한 부담 — 맛이 다소 진해서 물을 함께 마실 필요가 있음</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
     </row>
@@ -3583,17 +3639,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>초고함량 체력 및 활력 증진 — 6200mg 고함량 아르기닌으로 피로 회복과 운동 시 지구력을 높여줌</t>
+          <t>초고함량 활력 증진 — 고함량으로 운동 퍼포먼스 및 피로 회복 효과가 우수함</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>휴대 및 섭취의 편의성 — 하루 1포 개별 포장 형태로 들고 다니며 먹기 편함</t>
+          <t>1포 개별 포장 간편성 — 개별 포장되어 원하는 때 휴대하며 섭취하기 편함</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>고급스러운 선물 구성 — 쇼핑백과 추가 포가 동봉되어 선물용 패키지로 만족스러움</t>
+          <t>선물에 적합한 구성 — 전용 쇼핑백과 추가 증정이 있어 선물용으로 좋음</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -3603,7 +3659,7 @@
     <row r="20" ht="38" customHeight="1">
       <c r="B20" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -3611,56 +3667,56 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[한끼통살] 닭가슴살 한달 식단 패키지 30팩+(증정)보냉백</t>
+          <t>[좋은 아침 선물] 진저샷 미니보틀 8개입 (메시지 참 증정)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>타이거모닝</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>86,800원</t>
+          <t>29,900원</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/11566779</t>
+          <t>https://gift.kakao.com/product/13586002</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260429112212_3e1db89ad7174b6989286381ae7257c6.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260512190926_6c62df625cf44ea9ad3d7797fa43588b.jpg</t>
         </is>
       </c>
       <c r="I20" t="n">
         <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>151</v>
+        <v>11</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>높은 포만감과 뛰어난 맛 — 하나만 먹어도 속이 든든하며 다양한 맛이 훌륭함</t>
+          <t>상큼하고 매력적인 맛 — 생강과 과일이 조화되어 톡 쏘면서 상큼한 맛임</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>다양하고 알찬 식단 구성 — 종류가 다양하여 한 달 동안 질리지 않고 식단 관리 가능함</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
+          <t>아침 활력 충전 효과 — 공복이나 아침 섭취 시 눈이 뜨이고 에너지가 충전됨</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>귀여운 용기 디자인 — 보틀 디자인이 귀여워 자발적으로 손이 잘 감</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>오배송 및 문의 응대 미흡 — 제품 구성이 누락 및 중복 배송되었으나 문의 답변이 부족함</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>포장 터짐 및 소스 누출 — 팩 진공 포장이 헐렁하거나 터져서 소스가 묻어남</t>
-        </is>
-      </c>
+          <t>강한 맛으로 인한 호불호 — 생강 특유의 알싸한 맛 때문에 일부에게는 어려울 수 있음</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
     </row>
     <row r="21" ht="38" customHeight="1">
@@ -3705,17 +3761,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>다양한 베스트 제품 구성 — 음료, 쿠키 등 대표 제품을 1개씩 다채롭게 체험할 수 있음</t>
+          <t>다양한 체험형 구성 — 쿠키, 음료 등 베스트 제품을 골고루 맛볼 수 있음</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>고급스럽고 예쁜 패키지 — 포장 상태가 좋고 상자가 커서 선물 시 만족도가 높음</t>
+          <t>맛있는 프로틴 제품 — 단백질 제품 특유의 거부감 없이 맛이 훌륭함</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>간편한 휴대성과 뛰어난 맛 — 들고 다니기 편하며 음료와 쿠키 모두 맛이 우수함</t>
+          <t>고퀄리티 선물 포장 — 포장 패키지가 풍성하고 고급스러워 선물용으로 추천함</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3858,12 +3914,12 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
+          <t>홍삼/인삼</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
           <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -3915,22 +3971,22 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
+          <t>정관장</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
           <t>뉴트리포유</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>정관장</t>
-        </is>
-      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>옵티젠</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
           <t>센트룸</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>옵티젠</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -3972,22 +4028,22 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
+          <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
           <t>명품 비타민 뉴트리포유 듀얼+ 이뮨 종합 멀티비타민&amp;미네랄 7입+2입 증정 - 선물하기 단독 에디션</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
-        </is>
-      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>"한국인 맞춤 명품 비타민" 옵티젠 이뮨 멀티비타민&amp;미네랄 30입 / 1박스 (+GIFT 쇼핑백)</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
           <t>[센트룸] 맛있는 멀티비타민 미네랄 멀티구미 (80구미)</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>"한국인 맞춤 명품 비타민" 옵티젠 이뮨 멀티비타민&amp;미네랄 30입 / 1박스 (+GIFT 쇼핑백)</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -4052,19 +4108,19 @@
         <v>792</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>8716</v>
+        <v>1675</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1675</v>
+        <v>8718</v>
       </c>
       <c r="J7" s="3" t="n">
+        <v>211</v>
+      </c>
+      <c r="K7" s="3" t="n">
         <v>6486</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>211</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>771</v>
@@ -4078,68 +4134,75 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>선물용 만족도 높음 — 받는 사람의 기분을 좋게 하고 선물용으로 매우 만족스러움
-피로 회복 및 컨디션 개선 — 섭취 후 피로가 풀리고 컨디션과 면역력 회복에 도움을 줌</t>
+          <t>선물용 높은 만족도 — 받았을 때 기분이 좋아지고 선물하기에 매우 적합함
+피로 회복 및 건강 개선 — 무기력함이나 피로를 해소하고 건강 증진에 도움 됨
+꼼꼼하고 안전한 포장 — 제품 포장 상태가 잘되어 안전하게 도착함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>액상형으로 간편한 섭취 — 액상 제형이라 챙겨 먹기 쉽고 간편함
-활력 충전 및 피로 회복 — 피곤할 때 섭취 시 활력이 도는 듯한 느낌을 줌
-정성스러운 선물 구성 — 추석 카드와 추가 증정품이 포함되어 선물용으로 매우 만족스러움</t>
+          <t>간편한 액상형 섭취 — 액상 비타민이라 챙겨 먹기 쉽고 간편함
+활력 증진 및 피로 회복 — 복용 후 활력이 생기고 피로 해소에 도움이 됨
+고급스러운 선물 구성 — 패키지가 고급스럽고 메시지 카드 및 추가 증정이 있음</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>탁월한 피로 감소 효과 — 섭취 후 피곤함이 줄어들고 에너지를 얻는 데 도움을 줌
-고급스러운 선물 패키지 — 명절 케이스 디자인이 고급스러워 선물용으로 적합함</t>
+          <t>우수한 피로 회복 효과 — 섭취 후 피곤함이 줄고 에너지가 생기는 효과가 있음
+고급스러운 선물용 패키지 — 명절 및 생일 선물용으로 구성과 포장이 우수함</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>개별 포장의 편리함 — 한 포씩 포장되어 있어 책상이나 가방에 넣고 챙기기 용이함
-빠른 피로 회복 — 피로가 쌓였을 때 마시면 힘이 나고 피로가 풀림</t>
+          <t>개별 포장의 편의성 — 한 포씩 개별 포장되어 휴대하며 챙기기 편함
+체력 및 피로 개선 — 피로가 쌓였을 때 마시면 체력 회복과 힘이 생김
+고급스러운 포장 상태 — 포장 상태가 깔끔하고 고급스러워 선물용으로 적합함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>빠른 배송과 알찬 포장 — 배송이 빠르고 추가 종이봉투가 동봉되어 선물용으로 적합함
-컨디션 유지 및 활력 증진 — 여행이나 피로 시 섭취하면 활력이 생기고 하루 컨디션 유지에 좋음</t>
+          <t>신속한 배송 서비스 — 명절 연휴에도 배송이 빠르게 완료됨
+쇼핑백 포함 알찬 구성 — 추가 종이봉투와 쇼핑백이 포함되어 선물용으로 양호함
+컨디션 회복 효과 — 피로와 활력이 필요할 때 먹으면 하루 컨디션 유지에 좋음</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>빠른 에너징 및 체력 증진 — 섭취 후 피로감이 가시고 쌩쌩해질 정도로 체력 회복에 좋음
-꼼꼼한 포장과 휴대의 용이성 — 포장이 예쁘고 꼼꼼하며 휴대하며 챙겨 먹기 편함</t>
+          <t>예쁘고 고급스러운 포장 — 포장이 정성스럽고 고급스러워 지인 선물용으로 적합함
+높은 브랜드 신뢰도 — 정관장 브랜드라 품질을 믿고 구매 가능함
+맛과 섭취 편의성 — 개별 포장되어 섭취가 간편하고 맛도 우수함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>간편한 개별 포장 — 낱개로 개별 포장되어 있어 간편하게 챙겨 먹기 편리함
-브랜드 신뢰도 및 효과 — 정관장 브랜드 제품이라 신뢰가 가며 피로 회복 효과가 있음
-고급스러운 선물용 패키지 — 포장이 예쁘고 고급스러워 선물용으로 만족도가 높음</t>
+          <t>활력 및 에너지를 제공 — 섭취 후 피로가 줄고 생기 있게 활동하는 데 도움이 됨
+맛있는 오렌지 맛 — 오렌지 맛으로 맛있게 먹을 수 있어 거부감이 없음
+휴대성 및 꼼꼼한 포장 — 휴대가 용이하며 포장이 꼼꼼하게 도착함</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 맛과 간편한 식감 — 맛있는 젤리 형태라 거부감 없이 간식처럼 맛있게 섭취함
-물 없이 간편한 섭취 — 구미 제형이라 물 없이도 출근길이나 어디서나 먹기 편함</t>
+          <t>간편한 통합 섭취 방식 — 액상과 정제를 한 번에 마실 수 있어 아침에도 간편함
+체력 관리 및 피로 완화 — 잠이 부족하거나 체력이 떨어질 때 먹으면 효과적임
+정성스러운 패키징 — 정성스러운 선물 패키지로 구성되어 받는 사람 만족도가 높음</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>피로 완화 및 컨디션 관리 — 하루 하나씩 챙겨 먹으면 피로감이 줄어들고 건강 관리에 도움을 줌
-정성스러운 선물 구성 — 포장이 고급스럽고 빠른 배송과 구성으로 선물용에 만족함</t>
+          <t>맛있는 젤리 형태 — 영양제 느낌 없이 일반 젤리처럼 맛있게 먹을 수 있음
+물 없이 간편한 복용 — 구미 타입이라 물이 없어도 어디서나 챙겨 먹기 편리함
+귀엽고 깔끔한 패키지 — 패키지가 귀엽고 깔끔하여 가벼운 선물용으로 추천함</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>성별 맞춤 선택 가능 — 남성용과 여성용을 선택할 수 있어 기호에 맞춘 선물이 가능함
-지속적인 피로 완화 — 꾸준히 먹으면 피로감이 줄어들고 컨디션이 오래 유지됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+          <t>성별 맞춤 영양 설계 — 성별 옵션 선택이 가능하며 풍부한 영양 성분을 함유함
+깔끔하고 정성스러운 포장 — 정성이 담긴 깔끔한 포장으로 선물용 가치가 높음
+피로 해소 지속성 — 꾸준히 복용 시 덜 피곤하고 활력이 오래 유지됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
@@ -4147,32 +4210,38 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>부담스러운 가격 — 멀티비타민 가격이 다소 비싸게 느껴짐</t>
+          <t>다소 높은 가격 부담 — 가격이 다소 비싸서 직접 구매 시 부담이 있음</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>선물용 쇼핑백 불량 — 함께 전달된 쇼핑백이 훼손되어 그대로 사용하기 어려움</t>
+          <t>쇼핑백 품질 손상 — 함께 제공된 백이 훼손되어 받침으로 사용이 불가능함
+높은 가격대 형성 — 가격이 비싸서 본인 구매용으로는 부담이 큼</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>배송 요청사항 미반영 — 관리실 위탁 사전 요청에도 불구하고 문 앞에 두고 배송됨</t>
+          <t>배송 요청사항 미반영 — 관리실 위탁 요청에도 불구하고 문 앞에 두고 감</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>야간 복용 시 수면 방해 — 저녁 늦게 복용할 경우 숙면에 방해가 될 수 있음</t>
+        </is>
+      </c>
       <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>배송 상태 및 위생 불량 — 상자 및 쇼핑백에 먼지가 가득하거나 개봉 스티커에 손자국이 묻어 있음</t>
-        </is>
-      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>제품 먼지 오염 상태 — 택배 수령 시 쇼핑백과 상자에 먼지가 가득 묻어있음
+밀봉 스티커 훼손 문제 — 밀봉 스티커가 떼어졌다 붙은 자국과 이물질이 남아있음</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>다소 큰 알약 크기 — 기존 제품 대비 정제 크기가 커서 삼키기 다소 힘듦</t>
+          <t>큰 알약 제형 부담 — 기존 제품 대비 알약 크기가 커서 삼키기 다소 힘듦</t>
         </is>
       </c>
     </row>
@@ -4209,22 +4278,22 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
+          <t>33,000원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
           <t>19,900원</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>33,000원</t>
-        </is>
-      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>59,900원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
           <t>24,000원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>59,900원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -4392,27 +4461,27 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>피부/미용</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -4449,14 +4518,14 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
+          <t>그레인온</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
           <t>셀렉스</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>그레인온</t>
-        </is>
-      </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
           <t>아일로</t>
@@ -4469,7 +4538,7 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>타이거모닝</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -4506,14 +4575,14 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
+          <t>[리센느에디션] 베리말차 캡슐레이션 효소 1.8g 30포, 2개</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
           <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>[리센느에디션] 베리말차 캡슐레이션 효소 1.8g 30포, 2개</t>
-        </is>
-      </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
           <t>'1입 증정' 아일로 타입1 콜라겐 비오틴 앰플 14일분 오간자 에디션 + 앰플 1입 추가 증정</t>
@@ -4526,7 +4595,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>[한끼통살] 닭가슴살 한달 식단 패키지 30팩+(증정)보냉백</t>
+          <t>[좋은 아침 선물] 진저샷 미니보틀 8개입 (메시지 참 증정)</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -4591,10 +4660,10 @@
         <v>893</v>
       </c>
       <c r="G19" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="H19" s="3" t="n">
         <v>214</v>
-      </c>
-      <c r="H19" s="3" t="n">
-        <v>99</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>758</v>
@@ -4603,7 +4672,7 @@
         <v>248</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>151</v>
+        <v>11</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>15</v>
@@ -4617,69 +4686,74 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 패키지 디자인 — 틴케이스와 보자기, 박스 포장이 정성스럽고 예쁨
-비리지 않고 맛있는 제형 — 콜라겐 특유의 비린 맛이 없고 낱개 앰플 형태로 먹기 편함</t>
+          <t>화려하고 고급스러운 포장 — 보자기와 틴케이스 등 선물 포장이 매우 아름답고 정성스러움
+비리지 않고 맛있는 맛 — 콜라겐 특유의 비린 맛이 없고 맛있어서 부담 없음
+1병 단위 개별 포장 — 앰플 형태로 하나씩 따서 먹을 수 있어 간편함</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>우수한 가성비 — 저렴한 가격에 풍부한 수량을 구매할 수 있음
-부드러운 식감과 다양한 맛 — 닭가슴살이 부드럽고 맛이 다양하여 질리지 않고 식단 관리가 가능함</t>
+          <t>부드럽고 다양한 맛 — 식감이 부드럽고 질리지 않는 다양한 맛 구성임
+뛰어난 가성비 자랑 — 저렴한 가격에 많은 양을 구매할 수 있어 만족스러움</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>속 편한 소화 개선 — 식후 섭취 시 소화가 잘 되고 속이 편안해짐
-부담 없는 맛과 식감 — 고구마 맛 등으로 거부감 없이 맛있고 편하게 먹을 수 있음</t>
+          <t>속이 편한 소화 효과 — 식후 섭취 시 더부룩함이 없고 소화에 많은 도움이 됨
+고구마 맛의 우수한 풍미 — 거부감 없는 고소한 고구마 맛이라 먹기 편함
+풍성한 증정 및 방송 혜택 — 라이브 방송 및 행사 구매 시 혜택과 사은품이 훌륭함</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>속이 편안해지는 효소 효과 — 매일 한 포씩 먹으면 속이 편해지고 추천하기 좋음
-저렴한 가격과 알찬 구성 — 할인가로 부담 없이 구매 가능하며 사은품과 유통기한도 넉넉함</t>
+          <t>소화 개선 및 속 편함 — 꾸준히 섭취 시 속이 편안해져 만족도가 높음
+알찬 구성 및 긴 유통기한 — 유통기한이 넉넉하며 사은품과 가격 구성이 좋음
+정성 가득한 포장 — 포장에 정성이 느껴져 선물용으로 받거나 주기에 좋음</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>단백질 특유의 비린 맛 없음 — 비리거나 텁텁하지 않고 진한 초코우유처럼 맛있게 마실 수 있음
-든든한 포만감 제공 — 마신 뒤 포만감이 느껴져 운동 후나 허기질 때 간식용으로 좋음
-부드럽고 편안한 속 — 목넘김이 부드럽고 마신 후 속이 더부룩하지 않음</t>
+          <t>맛있는 맛과 식감 — 말차 맛이 고소하고 동봉된 단백질바도 맛이 양호함
+더부룩함 없는 소화 — 식단 관리나 식후 복용 시 속이 편안해짐
+만족스러운 사은품 구성 — 포토카드 및 단백질바 포함 구성의 가성비가 훌륭함</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>속 편한 소화 및 더부룩함 완화 — 섭취 후 더부룩한 속이 편안해지는 느낌을 받음
-고소하고 맛있는 맛 — 베리말차 맛이 고소하고 맛있어 간편하게 먹기 좋음</t>
+          <t>비리지 않은 달콤한 맛 — 단백질 음료 특유의 비린 맛과 텁텁함이 없음
+부드러운 목넘김과 포만감 — 목넘김이 부드럽고 적당한 포만감을 제공함
+슬림한 용기의 휴대성 — 패키지가 슬림하여 가방에 넣어 다니기 편리함</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>고급스럽고 예쁜 포장 — 앰플 용기와 박스 포장이 예쁘고 고급스러움
-부담 없는 맛있는 제형 — 비타민 음료처럼 맛이 좋아 거부감 없이 마실 수 있음</t>
+          <t>고급스러운 앰플 디자인 — 용기와 포장이 공주풍으로 고급스럽고 예쁨
+알약 대비 쉬운 섭취 — 앰플 형태로 알약을 먹기 힘들어하는 사람에게 편함</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>초고함량 체력 및 활력 증진 — 6200mg 고함량 아르기닌으로 피로 회복과 운동 시 지구력을 높여줌
-휴대 및 섭취의 편의성 — 하루 1포 개별 포장 형태로 들고 다니며 먹기 편함
-고급스러운 선물 구성 — 쇼핑백과 추가 포가 동봉되어 선물용 패키지로 만족스러움</t>
+          <t>초고함량 활력 증진 — 고함량으로 운동 퍼포먼스 및 피로 회복 효과가 우수함
+1포 개별 포장 간편성 — 개별 포장되어 원하는 때 휴대하며 섭취하기 편함
+선물에 적합한 구성 — 전용 쇼핑백과 추가 증정이 있어 선물용으로 좋음</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>높은 포만감과 뛰어난 맛 — 하나만 먹어도 속이 든든하며 다양한 맛이 훌륭함
-다양하고 알찬 식단 구성 — 종류가 다양하여 한 달 동안 질리지 않고 식단 관리 가능함</t>
+          <t>상큼하고 매력적인 맛 — 생강과 과일이 조화되어 톡 쏘면서 상큼한 맛임
+아침 활력 충전 효과 — 공복이나 아침 섭취 시 눈이 뜨이고 에너지가 충전됨
+귀여운 용기 디자인 — 보틀 디자인이 귀여워 자발적으로 손이 잘 감</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>다양한 베스트 제품 구성 — 음료, 쿠키 등 대표 제품을 1개씩 다채롭게 체험할 수 있음
-고급스럽고 예쁜 패키지 — 포장 상태가 좋고 상자가 커서 선물 시 만족도가 높음
-간편한 휴대성과 뛰어난 맛 — 들고 다니기 편하며 음료와 쿠키 모두 맛이 우수함</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="60" customHeight="1">
+          <t>다양한 체험형 구성 — 쿠키, 음료 등 베스트 제품을 골고루 맛볼 수 있음
+맛있는 프로틴 제품 — 단백질 제품 특유의 거부감 없이 맛이 훌륭함
+고퀄리티 선물 포장 — 포장 패키지가 풍성하고 고급스러워 선물용으로 추천함</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
       <c r="B21" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
@@ -4687,32 +4761,31 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>부담스러운 가격대 — 제품 가격이 다소 비싸고 지속해서 가격이 상승함</t>
+          <t>가격대에 대한 부담 — 지속적인 가격 상승 및 기본 가격대가 비싼 편임</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>배송 중 해동 발생 — 냉동 상품이 유지되지 않고 전부 녹아서 배송됨</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>증정품 크기 아쉬움 — 증정된 단백질칩 사은품의 크기가 다소 작음</t>
-        </is>
-      </c>
+          <t>배송 중 해동 발생 — 배송을 받았을 때 제품이 녹아있는 상태였음</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>배송 지연 아쉬움 — 배송이 다소 늦게 도착함</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>다소 느린 배송 속도 — 배송 진행 속도가 다소 늦어 아쉬움이 있음</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>진한 맛에 대한 부담 — 맛이 다소 진해서 물을 함께 마실 필요가 있음</t>
+        </is>
+      </c>
       <c r="J21" s="3" t="inlineStr"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>오배송 및 문의 응대 미흡 — 제품 구성이 누락 및 중복 배송되었으나 문의 답변이 부족함
-포장 터짐 및 소스 누출 — 팩 진공 포장이 헐렁하거나 터져서 소스가 묻어남</t>
+          <t>강한 맛으로 인한 호불호 — 생강 특유의 알싸한 맛 때문에 일부에게는 어려울 수 있음</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr"/>
@@ -4745,14 +4818,14 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
+          <t>24,900원</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
           <t>28,900원</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>24,900원</t>
-        </is>
-      </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
           <t>32,900원</t>
@@ -4765,7 +4838,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>86,800원</t>
+          <t>29,900원</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -4960,7 +5033,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4968,7 +5041,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>대웅제약 식물성 뉴티지 오메가3 30캡슐 30일분</t>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4978,31 +5051,35 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000203&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000131&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20251202/7FdyxsWTlcbRJnDROGoC600000203_00_007FdyxsWTlcbRJnDROGoC.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/rCiQaBH4VQ1rKKr7rz83600000131_00_00rCiQaBH4VQ1rKKr7rz83.png</t>
         </is>
       </c>
       <c r="I2" t="n">
         <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>1591</v>
+        <v>4772</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>압도적인 가성비 — 저렴한 가격으로 서브용 영양제로 부담 없이 지속 구매 가능함</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>부담 없는 착한 가격 — 가격대가 저렴하여 부담 없이 구매하기 좋음</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>꾸준한 재구매 만족도 — 제품 만족도가 높아 꾸준히 재구매로 이어짐</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -5019,43 +5096,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>대웅제약 칼슘 120정 30일분</t>
+          <t>종근당 데일리와이즈 푸룬 구미 7일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>종근당</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000147&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306208&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250409/7vBQfmyyR1zN9NfVg993600000147_00_007vBQfmyyR1zN9NfVg993.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260417/wEewWmXsoUl4j1ERyFu9032306208_00_01wEewWmXsoUl4j1ERyFu9.jpg</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J3" t="n">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>부담 없는 저렴한 가격 — 가격 대비 구성이 알차 뼈 건강 관리용으로 구매하기 좋음</t>
+          <t>맛있는 구미 제형 — 맛이 좋아서 남녀노소 즐겁게 먹을 수 있음</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>용량 관련 오인 가능성 — 1일 권장량이 표기되어 있으나 한 번에 다 먹기 쉬움</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
@@ -5070,41 +5151,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
+          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>1,500원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000131&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253277&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/rCiQaBH4VQ1rKKr7rz83600000131_00_00rCiQaBH4VQ1rKKr7rz83.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260422/eIhoZ9JSC5jbp33vSbZX987253277_00_01eIhoZ9JSC5jbp33vSbZX.jpg</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>4770</v>
+        <v>762</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>착한 가격과 혈당 관리 — 저렴한 가격으로 식전 챙겨 먹으며 혈당 관리에 활용함</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>운동 전 기력 충전 — 운동이나 일하기 전에 먹으면 기력이 생기는 효과가 있음</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>상큼한 맛과 가성비 — 음료처럼 상큼한 맛이며 가성비가 훌륭함</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
@@ -5113,7 +5198,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -5121,43 +5206,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[김우빈 PICK] 종근당건강 아임비타 비타민B 2000 30정 30일분</t>
+          <t>대웅제약 코엔자임Q10 6캡슐 6일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591581091&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000279&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260601/30NEHOm4dIOnmUVwUKLJ591581091_00_0030NEHOm4dIOnmUVwUKLJ.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260504/OqWOmDxWU1qoZh2gUZfq600000279_00_01OqWOmDxWU1qoZh2gUZfq.png</t>
         </is>
       </c>
       <c r="I5" t="n">
         <v>4.8</v>
       </c>
       <c r="J5" t="n">
-        <v>509</v>
+        <v>335</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>PTP 개별 포장의 위생성 — 개별 포장으로 위생적이며 보관이 편함</t>
+          <t>소량 구매의 편의성 — 급할 때나 필요할 때 소량 단위로 사기 편함</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>언제든 부담 없는 가격 — 30일분을 5,000원에 항시 저렴하게 구매 가능함</t>
+          <t>깔끔한 제품 디자인 — 디자인이 깔끔하여 누구나 사용하기 무난함</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -5176,7 +5261,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대웅제약 쏘팔메토 옥타코사놀 30캡슐 30일분</t>
+          <t>대웅제약 녹차카테킨 30정 30일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5191,28 +5276,40 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000139&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000136&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/Am2C7Da2wracg1TigkAF600000139_00_00Am2C7Da2wracg1TigkAF.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/5KgtE2Z5pfS6P1gIBIIh600000136_00_005KgtE2Z5pfS6P1gIBIIh.png</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>2335</v>
+        <v>3654</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>저렴한 사전 관리용 제품 — 가격이 매우 저렴해 부담 없이 꾸준히 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>목넘김 편한 작은 알약 — 알약 크기가 작아서 복용할 때 부담이 없음</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>탄수화물 소화 보조 — 탄수화물 섭취 시 소화가 잘되는 느낌을 받음</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>지속 구매하기 좋은 가성비 — 저렴한 가격으로 지속해서 재구매하기 편함</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>효과 체감의 개인차 — 사람에 따라 효과를 뚜렷하게 느끼지 못할 수 있음</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
@@ -5227,12 +5324,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
+          <t>동국제약 마데카 리포좀 레티놀C 20포</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>이너뷰 바이 리튠</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -5242,31 +5339,35 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953534&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910601&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250627/7ii4aNyp1XbM6AH8HjHT994953534_00_007ii4aNyp1XbM6AH8HjHT.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250502/YBmj8aPscGIkmB6O6RuJ610910601_00_00YBmj8aPscGIkmB6O6RuJ.jpg</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>1306</v>
+        <v>635</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>자극적 음식 후 붓기 완화 — 짠 음식 섭취 후 마시면 붓기가 풀리는 효과를 느낌</t>
+          <t>상큼하고 맛있는 맛 — 생각보다 맛있고 상큼해서 매일 먹기 좋음</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>청량하고 맛있는 음료 맛 — 이온음료 맛이 나서 얼음물에 타 마시면 상큼하고 맛있음</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>착한 가격 및 가성비 — 가격이 착해서 다회 재구매하기에 부담이 없음</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>간편한 섭취 방식 — 포 단위로 되어 있어 편리하게 섭취 가능함</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -5274,7 +5375,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5282,54 +5383,58 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 진한 레드 석류 콜라겐 7포</t>
+          <t>종근당 데일리와이즈 혈당컷 다이어트 12정 12일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>이너뷰 바이 리튠</t>
+          <t>종근당</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953529&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306201&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250627/vXg1N5D0xbSNweDPvvl2994953529_00_00vXg1N5D0xbSNweDPvvl2.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260406/NBw0phjtTvR7tEfBicGr032306201_00_01NBw0phjtTvR7tEfBicGr.jpg</t>
         </is>
       </c>
       <c r="I8" t="n">
         <v>4.7</v>
       </c>
       <c r="J8" t="n">
-        <v>359</v>
+        <v>1256</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>진하고 맛있는 석류 맛 — 석류 맛이 진해 맛있게 먹을 수 있음</t>
+          <t>저렴한 구매 가격 — 저렴한 가격으로 부담 없이 구매할 수 있음</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>저렴하고 간편한 섭취 — 가격이 저렴하고 한 포씩 챙겨 먹기 편함</t>
+          <t>무난한 복용감 — 매일 챙겨 먹기에 무난함</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>타 약물 병용 시 주의 — 복용 중인 다른 약물이 있다면 주의가 필요함</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5337,12 +5442,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>동국 맛있는 샐러드 미니볼 15포 15일분</t>
+          <t>대웅제약 루테인 30정 30일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -5352,32 +5457,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910891&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000126&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260312/tgDz0oHoOLB3gj3BLgFd610910891_00_01tgDz0oHoOLB3gj3BLgFd.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/u8Kxfk5gV3uvRKBRNTM6600000126_00_00u8Kxfk5gV3uvRKBRNTM6.png</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>2202</v>
+        <v>4005</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>간편한 간식 대체 — 달달한 맛으로 샐러드 대신 간편하게 챙겨 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>뛰어난 가성비 — 저렴한 가격으로 눈 건강 관리가 가능함</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>간편한 지속 복용 — 간편하게 꾸준히 복용하기에 좋음</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>지나치게 딱딱한 식감 — 볼 제형이 너무 단단하여 씹을 때 치아에 부담이 됨</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
@@ -5392,12 +5497,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[의약외품] 동화 퀵앤써액 샤인머스캣 12ml 5포</t>
+          <t>대웅제약 비타민B 30정 30일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -5407,28 +5512,28 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618635&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000129&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260424/KoucQ3ocL5x28bXaWKvV601618635_00_00KoucQ3ocL5x28bXaWKvV.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/5QghHD5oyZssCfnGZbzA600000129_00_005QghHD5oyZssCfnGZbzA.png</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>598</v>
+        <v>2204</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>간편한 휴대성과 맛 — 어디서나 들고 다니기 좋고 맛있게 마실 수 있음</t>
+          <t>극강의 가격 경쟁력 — 3,000원이라는 매우 저렴한 가격에 판매함</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>피로 완화에 도움 — 체력이 떨어졌을 때 먹으면 피로감이 감소함</t>
+          <t>온 가족 함께 복용 — 온 가족이 함께 늘 챙겨 먹기 적합함</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -5439,7 +5544,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5447,12 +5552,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>대웅제약 비타민C 30정 30일분</t>
+          <t>자연관 정성담은 배도라지스틱 12포</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>자연관</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -5462,28 +5567,36 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000127&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=901762093&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/V0qSVbLLgSaCWbYWEu73600000127_00_00V0qSVbLLgSaCWbYWEu73.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260508/SdledEzpIdjdFFQW6W8g901762093_00_00SdledEzpIdjdFFQW6W8g.png</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J11" t="n">
-        <v>2691</v>
+        <v>887</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>긴 소비기한과 저렴함 — 소비기한이 넉넉하고 저렴하여 일상에서 사먹기 편함</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>우수한 가성비 제공 — 가격 대비 구성과 용량이 매우 우수함</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>달콤하고 맛있는 풍미 — 달고 맛이 좋아 목 기관지 관리에 자주 구매함</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>맛에 대한 호불호 — 배도라지 특유의 맛이 익숙하지 않으면 먹기 힘들 수 있음</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
@@ -5598,52 +5711,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
           <t>루테인/눈건강</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
         </is>
       </c>
     </row>
@@ -5660,47 +5773,47 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>종근당</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>익스트림</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>종근당건강</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>동국제약</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>종근당</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>이너뷰 바이 리튠</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>이너뷰 바이 리튠</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>동국제약</t>
-        </is>
-      </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>자연관</t>
         </is>
       </c>
     </row>
@@ -5712,52 +5825,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 식물성 뉴티지 오메가3 30캡슐 30일분</t>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 칼슘 120정 30일분</t>
+          <t>종근당 데일리와이즈 푸룬 구미 7일분</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
+          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>[김우빈 PICK] 종근당건강 아임비타 비타민B 2000 30정 30일분</t>
+          <t>대웅제약 코엔자임Q10 6캡슐 6일분</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 쏘팔메토 옥타코사놀 30캡슐 30일분</t>
+          <t>대웅제약 녹차카테킨 30정 30일분</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
+          <t>동국제약 마데카 리포좀 레티놀C 20포</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 진한 레드 석류 콜라겐 7포</t>
+          <t>종근당 데일리와이즈 혈당컷 다이어트 12정 12일분</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>동국 맛있는 샐러드 미니볼 15포 15일분</t>
+          <t>대웅제약 루테인 30정 30일분</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>[의약외품] 동화 퀵앤써액 샤인머스캣 12ml 5포</t>
+          <t>대웅제약 비타민B 30정 30일분</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 비타민C 30정 30일분</t>
+          <t>자연관 정성담은 배도라지스틱 12포</t>
         </is>
       </c>
     </row>
@@ -5771,7 +5884,7 @@
         <v>4.8</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>4.8</v>
@@ -5789,13 +5902,13 @@
         <v>4.7</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="7">
@@ -5805,37 +5918,37 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1591</v>
+        <v>4772</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>4770</v>
+        <v>762</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>509</v>
+        <v>335</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>2335</v>
+        <v>3654</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1306</v>
+        <v>635</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>359</v>
+        <v>1256</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>2202</v>
+        <v>4005</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>598</v>
+        <v>2204</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>2691</v>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -5843,56 +5956,63 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>압도적인 가성비 — 저렴한 가격으로 서브용 영양제로 부담 없이 지속 구매 가능함</t>
+          <t>부담 없는 착한 가격 — 가격대가 저렴하여 부담 없이 구매하기 좋음
+꾸준한 재구매 만족도 — 제품 만족도가 높아 꾸준히 재구매로 이어짐</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>부담 없는 저렴한 가격 — 가격 대비 구성이 알차 뼈 건강 관리용으로 구매하기 좋음</t>
+          <t>맛있는 구미 제형 — 맛이 좋아서 남녀노소 즐겁게 먹을 수 있음</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>착한 가격과 혈당 관리 — 저렴한 가격으로 식전 챙겨 먹으며 혈당 관리에 활용함</t>
+          <t>운동 전 기력 충전 — 운동이나 일하기 전에 먹으면 기력이 생기는 효과가 있음
+상큼한 맛과 가성비 — 음료처럼 상큼한 맛이며 가성비가 훌륭함</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>PTP 개별 포장의 위생성 — 개별 포장으로 위생적이며 보관이 편함
-언제든 부담 없는 가격 — 30일분을 5,000원에 항시 저렴하게 구매 가능함</t>
+          <t>소량 구매의 편의성 — 급할 때나 필요할 때 소량 단위로 사기 편함
+깔끔한 제품 디자인 — 디자인이 깔끔하여 누구나 사용하기 무난함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>저렴한 사전 관리용 제품 — 가격이 매우 저렴해 부담 없이 꾸준히 먹기 좋음</t>
+          <t>목넘김 편한 작은 알약 — 알약 크기가 작아서 복용할 때 부담이 없음
+탄수화물 소화 보조 — 탄수화물 섭취 시 소화가 잘되는 느낌을 받음
+지속 구매하기 좋은 가성비 — 저렴한 가격으로 지속해서 재구매하기 편함</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>자극적 음식 후 붓기 완화 — 짠 음식 섭취 후 마시면 붓기가 풀리는 효과를 느낌
-청량하고 맛있는 음료 맛 — 이온음료 맛이 나서 얼음물에 타 마시면 상큼하고 맛있음</t>
+          <t>상큼하고 맛있는 맛 — 생각보다 맛있고 상큼해서 매일 먹기 좋음
+착한 가격 및 가성비 — 가격이 착해서 다회 재구매하기에 부담이 없음
+간편한 섭취 방식 — 포 단위로 되어 있어 편리하게 섭취 가능함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>진하고 맛있는 석류 맛 — 석류 맛이 진해 맛있게 먹을 수 있음
-저렴하고 간편한 섭취 — 가격이 저렴하고 한 포씩 챙겨 먹기 편함</t>
+          <t>저렴한 구매 가격 — 저렴한 가격으로 부담 없이 구매할 수 있음
+무난한 복용감 — 매일 챙겨 먹기에 무난함</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>간편한 간식 대체 — 달달한 맛으로 샐러드 대신 간편하게 챙겨 먹기 좋음</t>
+          <t>뛰어난 가성비 — 저렴한 가격으로 눈 건강 관리가 가능함
+간편한 지속 복용 — 간편하게 꾸준히 복용하기에 좋음</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>간편한 휴대성과 맛 — 어디서나 들고 다니기 좋고 맛있게 마실 수 있음
-피로 완화에 도움 — 체력이 떨어졌을 때 먹으면 피로감이 감소함</t>
+          <t>극강의 가격 경쟁력 — 3,000원이라는 매우 저렴한 가격에 판매함
+온 가족 함께 복용 — 온 가족이 함께 늘 챙겨 먹기 적합함</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>긴 소비기한과 저렴함 — 소비기한이 넉넉하고 저렴하여 일상에서 사먹기 편함</t>
+          <t>우수한 가성비 제공 — 가격 대비 구성과 용량이 매우 우수함
+달콤하고 맛있는 풍미 — 달고 맛이 좋아 목 기관지 관리에 자주 구매함</t>
         </is>
       </c>
     </row>
@@ -5903,19 +6023,31 @@
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>용량 관련 오인 가능성 — 1일 권장량이 표기되어 있으나 한 번에 다 먹기 쉬움</t>
+        </is>
+      </c>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>효과 체감의 개인차 — 사람에 따라 효과를 뚜렷하게 느끼지 못할 수 있음</t>
+        </is>
+      </c>
       <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>지나치게 딱딱한 식감 — 볼 제형이 너무 단단하여 씹을 때 치아에 부담이 됨</t>
-        </is>
-      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>타 약물 병용 시 주의 — 복용 중인 다른 약물이 있다면 주의가 필요함</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>맛에 대한 호불호 — 배도라지 특유의 맛이 익숙하지 않으면 먹기 힘들 수 있음</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -5925,37 +6057,37 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>1,000원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>1,500원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>1,000원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>3,000원</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -6149,7 +6281,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -6157,27 +6289,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[딥트3일/남규리PICK]남규리의 바른 효소 리셋 8포</t>
+          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>딥트3일</t>
+          <t>바이오코어유산균</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>16,000원</t>
+          <t>12,900원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000211396&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000200143&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021139617ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020014347ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -6192,7 +6324,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -6200,51 +6332,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
+          <t>리부트 유산균 젤리 27g*6포 (6일분)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>바이오코어유산균</t>
+          <t>리부트</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>12,900원</t>
+          <t>14,000원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000200143&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000236947&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020014347ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J3" t="n">
-        <v>12670</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>속 편한 장 건강 관리 — 배 아픔 없이 원활한 배변 활동을 도와줌</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>귀여운 산리오 콜라보 증정품 — 러기지택 등 캐릭터 구성품이 포함되어 만족도가 높음</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023694706ko.png?l=ko</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>다소 큰 알약 크기 — 기존 유산균에 비해 알약 크기가 살짝 크게 느껴짐</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
@@ -6259,27 +6375,27 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[9월 올영픽] 박카스O액 5병 기획 (+1병) (+폼폼푸린 쉐이크 키링) (6일분)</t>
+          <t>[딥트3일/남규리PICK]남규리의 바른 효소 리셋 8포</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>박카스</t>
+          <t>딥트3일</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10,900원</t>
+          <t>16,000원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000263484&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000211396&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026348402ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021139617ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -6294,7 +6410,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -6302,27 +6418,27 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
+          <t>[올영단독] 지노마스터 질유산균 70캡슐 (70일분)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>판도라</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>24,700원</t>
+          <t>59,000원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000227334&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000249509&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022733451ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024950901ko.png?l=ko</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -6337,7 +6453,7 @@
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -6345,45 +6461,33 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[저분자] 빌드 프리미엄 테프 발효 효소 30포 (1개월분)</t>
+          <t>[9월 올영픽] 콜레올로지 컷 다이어트 유산균 14캡슐 (+마이멜로디 카라비너) (10일분) / 20캡슐</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>빌드</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>18,900원</t>
+          <t>18,700원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000219379&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000229934&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021937922ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>20331</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>고소한 인절미 맛과 고운 입자 — 특유의 쿰쿰함이 없고 입자가 고와서 고소하게 먹기 편함</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>식후 체중 및 탄수화물 관리 — 탄수화물 식사 후 먹기 좋으며 체중 관리에 도움이 됨</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022993425ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -6423,22 +6527,10 @@
           <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J7" t="n">
-        <v>8230</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>알찬 구성과 굿즈 증정 — 2개월 기획 구성에 키링이나 포토카드 등이 포함되어 만족함</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>하루 한 알의 간편함 — 아침 공복에 1캡슐씩 물과 함께 간단히 먹기 좋음</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -6455,7 +6547,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[9월 올영픽] 콜레올로지 컷 다이어트 유산균 14캡슐 (+마이멜로디 카라비너) (10일분) / 20캡슐</t>
+          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -6465,17 +6557,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>18,700원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000229934&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000175634&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022993425ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017563488ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -6490,7 +6582,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -6498,33 +6590,45 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>[저분자] 빌드 프리미엄 테프 발효 효소 30포 (1개월분)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>빌드</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>39,800원</t>
+          <t>18,900원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000219379&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021937922ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>20339</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>고소하고 고운 입자 — 입자가 고와 섭취가 편하고 쿰쿰함 없는 인절미맛임</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>체중 조절 도움 — 탄수화물 섭취가 많은 사람의 체중 조절에 유용함</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -6541,27 +6645,27 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[9월 올영픽/산리오콜라보] CJ 이너비 브이 캔디 14포 (+마이멜로디 마그넷액자)</t>
+          <t>[9월 올영픽] 박카스O액 5병 기획 (+1병) (+폼폼푸린 쉐이크 키링) (6일분)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CJ이너비</t>
+          <t>박카스</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>11,400원</t>
+          <t>10,900원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000264048&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000263484&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026404813ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026348402ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -6576,7 +6680,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -6584,27 +6688,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>75,000원</t>
+          <t>30,400원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000193086&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019308652ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -6727,52 +6831,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
     </row>
@@ -6784,52 +6888,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>바이오코어유산균</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>리부트</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>딥트3일</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>바이오코어유산균</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>지노마스터</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>푸드올로지</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>푸드올로지</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>빌드</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>박카스</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>판도라</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>빌드</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>덴프스</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>푸드올로지</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>프로뉴트리션</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>CJ이너비</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>오쏘몰</t>
         </is>
       </c>
     </row>
@@ -6841,52 +6945,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>리부트 유산균 젤리 27g*6포 (6일분)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>[딥트3일/남규리PICK]남규리의 바른 효소 리셋 8포</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>[올영단독] 지노마스터 질유산균 70캡슐 (70일분)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>[9월 올영픽] 콜레올로지 컷 다이어트 유산균 14캡슐 (+마이멜로디 카라비너) (10일분) / 20캡슐</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>[저분자] 빌드 프리미엄 테프 발효 효소 30포 (1개월분)</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>[9월 올영픽] 박카스O액 5병 기획 (+1병) (+폼폼푸린 쉐이크 키링) (6일분)</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>[저분자] 빌드 프리미엄 테프 발효 효소 30포 (1개월분)</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>[9월 올영픽] 콜레올로지 컷 다이어트 유산균 14캡슐 (+마이멜로디 카라비너) (10일분) / 20캡슐</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>[9월 올영픽/산리오콜라보] CJ 이너비 브이 캔디 14포 (+마이멜로디 마그넷액자)</t>
-        </is>
-      </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
     </row>
@@ -6897,19 +7001,15 @@
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="3" t="n">
-        <v>4.8</v>
-      </c>
+      <c r="D6" s="3" t="inlineStr"/>
       <c r="E6" s="3" t="inlineStr"/>
       <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="n">
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="H6" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="I6" s="3" t="inlineStr"/>
-      <c r="J6" s="3" t="inlineStr"/>
       <c r="K6" s="3" t="inlineStr"/>
       <c r="L6" s="3" t="inlineStr"/>
     </row>
@@ -6920,19 +7020,15 @@
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="n">
-        <v>12670</v>
-      </c>
+      <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="n">
-        <v>20331</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>8230</v>
-      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="n">
+        <v>20339</v>
+      </c>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
     </row>
@@ -6943,28 +7039,18 @@
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>속 편한 장 건강 관리 — 배 아픔 없이 원활한 배변 활동을 도와줌
-귀여운 산리오 콜라보 증정품 — 러기지택 등 캐릭터 구성품이 포함되어 만족도가 높음</t>
-        </is>
-      </c>
+      <c r="D8" s="3" t="inlineStr"/>
       <c r="E8" s="3" t="inlineStr"/>
       <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>고소한 인절미 맛과 고운 입자 — 특유의 쿰쿰함이 없고 입자가 고와서 고소하게 먹기 편함
-식후 체중 및 탄수화물 관리 — 탄수화물 식사 후 먹기 좋으며 체중 관리에 도움이 됨</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>알찬 구성과 굿즈 증정 — 2개월 기획 구성에 키링이나 포토카드 등이 포함되어 만족함
-하루 한 알의 간편함 — 아침 공복에 1캡슐씩 물과 함께 간단히 먹기 좋음</t>
-        </is>
-      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>고소하고 고운 입자 — 입자가 고와 섭취가 편하고 쿰쿰함 없는 인절미맛임
+체중 조절 도움 — 탄수화물 섭취가 많은 사람의 체중 조절에 유용함</t>
+        </is>
+      </c>
       <c r="K8" s="3" t="inlineStr"/>
       <c r="L8" s="3" t="inlineStr"/>
     </row>
@@ -6975,11 +7061,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>다소 큰 알약 크기 — 기존 유산균에 비해 알약 크기가 살짝 크게 느껴짐</t>
-        </is>
-      </c>
+      <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
@@ -6997,52 +7079,52 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>12,900원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>14,000원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
           <t>16,000원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>12,900원</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>59,000원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>18,700원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>31,900원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>17,900원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>18,900원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>10,900원</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>24,700원</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>18,900원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>31,900원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>18,700원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>39,800원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>11,400원</t>
-        </is>
-      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>75,000원</t>
+          <t>30,400원</t>
         </is>
       </c>
     </row>
@@ -7172,19 +7254,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>37.5</v>
+        <v>32.5</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -7194,16 +7276,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>22.5</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>
@@ -7216,10 +7298,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>22.5</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
         <v>8</v>
@@ -7228,45 +7310,45 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -7278,7 +7360,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -7288,19 +7370,19 @@
         <v>2.5</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="B8" t="n">
